--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-laborbereich.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-laborbereich.xlsx
@@ -202,7 +202,7 @@
     <t>26436-6</t>
   </si>
   <si>
-    <t>LABORATORY STUDIES</t>
+    <t>Laboratory studies (set)</t>
   </si>
   <si>
     <t>26437-4</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-laborbereich.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-laborbereich.xlsx
@@ -106,97 +106,97 @@
     <t>18717-9</t>
   </si>
   <si>
-    <t>BLOOD BANK STUDIES</t>
+    <t>Blood bank studies (set)</t>
   </si>
   <si>
     <t>18718-7</t>
   </si>
   <si>
-    <t>CELL MARKER STUDIES</t>
+    <t>Cell marker studies (set)</t>
   </si>
   <si>
     <t>18719-5</t>
   </si>
   <si>
-    <t>CHEMISTRY STUDIES</t>
+    <t>Chemistry studies (set)</t>
   </si>
   <si>
     <t>18720-3</t>
   </si>
   <si>
-    <t>COAGULATION STUDIES</t>
+    <t>Coagulation studies (set)</t>
   </si>
   <si>
     <t>18721-1</t>
   </si>
   <si>
-    <t>THERAPEUTIC DRUG MONITORING STUDIES</t>
+    <t>Therapeutic drug monitoring studies (set)</t>
   </si>
   <si>
     <t>18722-9</t>
   </si>
   <si>
-    <t>FERTILITY STUDIES</t>
+    <t>Fertility studies (set)</t>
   </si>
   <si>
     <t>18723-7</t>
   </si>
   <si>
-    <t>HEMATOLOGY STUDIES</t>
+    <t>Hematology studies (set)</t>
   </si>
   <si>
     <t>18724-5</t>
   </si>
   <si>
-    <t>HLA STUDIES</t>
+    <t>HLA studies (set)</t>
   </si>
   <si>
     <t>18725-2</t>
   </si>
   <si>
-    <t>MICROBIOLOGY STUDIES</t>
+    <t>Microbiology studies (set)</t>
   </si>
   <si>
     <t>18727-8</t>
   </si>
   <si>
-    <t>SEROLOGY STUDIES</t>
+    <t>Serology studies (set)</t>
   </si>
   <si>
     <t>18728-6</t>
   </si>
   <si>
-    <t>TOXICOLOGY STUDIES</t>
+    <t>Toxicology studies (set)</t>
   </si>
   <si>
     <t>18729-4</t>
   </si>
   <si>
-    <t>URINALYSIS STUDIES</t>
+    <t>Urinalysis studies (set)</t>
   </si>
   <si>
     <t>18767-4</t>
   </si>
   <si>
-    <t>BLOOD GAS STUDIES</t>
+    <t>Blood gas studies (set)</t>
   </si>
   <si>
     <t>18768-2</t>
   </si>
   <si>
-    <t>CELL COUNTS+DIFFERENTIAL STUDIES</t>
+    <t>Cell counts+Differential studies (set)</t>
   </si>
   <si>
     <t>18769-0</t>
   </si>
   <si>
-    <t>MICROBIAL SUSCEPTIBILITY TESTS</t>
+    <t>Microbial susceptibility tests Set</t>
   </si>
   <si>
     <t>26435-8</t>
   </si>
   <si>
-    <t>MOLECULAR PATHOLOGY STUDIES</t>
+    <t>Molecular pathology studies (set)</t>
   </si>
   <si>
     <t>26436-6</t>
@@ -208,13 +208,13 @@
     <t>26437-4</t>
   </si>
   <si>
-    <t>CHEMISTRY CHALLENGE STUDIES</t>
+    <t>Chemistry challenge studies (set)</t>
   </si>
   <si>
     <t>26438-2</t>
   </si>
   <si>
-    <t>CYTOLOGY STUDIES</t>
+    <t>Cytology studies (set)</t>
   </si>
   <si>
     <t/>
